--- a/2022 data/excel_outputs/48_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/48_boothwise_data.xlsx
@@ -14,11 +14,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="398">
   <si>
     <t>AC 48 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -148,7 +223,7 @@
     <t>BHAI JOGA SINGH PUBLIC SCHOOL ROOM NO.1 DEVPURI</t>
   </si>
   <si>
-    <t>##0 ##0 ###### ##### #0##0.1 ##### ##### ###</t>
+    <t>VARDHMAN ACADEMY ROOM NO.2 RAILWAY ROAD</t>
   </si>
   <si>
     <t>D.N. DEGREE COLLEGE ROOM NO.2 CHOPLA RAILWARY ROAD</t>
@@ -172,9 +247,6 @@
     <t>VARDHMAN ACADEMY ROOM NO.1 RAILWAY ROAD</t>
   </si>
   <si>
-    <t>VARDHMAN ACADEMY ROOM NO.2 RAILWAY ROAD</t>
-  </si>
-  <si>
     <t>SIR CHHOTU RAM INSTITUTE OF ENGINEERING AND TECHNOLOGY ROOM NO. 1 CANTEEN JAIL CHUNGI</t>
   </si>
   <si>
@@ -787,7 +859,7 @@
     <t>ADITYA PUBLIC SCHOOL ROOM NO.1 MASTER COLONY GALI NO.7</t>
   </si>
   <si>
-    <t>###### #0##### #0 ##0.2 ###### ###### ### ##0 7</t>
+    <t>TOWN HALL UTTAR PURV ROOM NO.2 NEAR GHANTAGHAR</t>
   </si>
   <si>
     <t>ADITYA PUBLIC SCHOOL ROOM NO.3 MASTER COLONY GALI NO.7</t>
@@ -871,9 +943,6 @@
     <t>TOWN HALL UTTAR PURV ROOM NO.1 NEAR GHANTAGHAR</t>
   </si>
   <si>
-    <t>TOWN HALL UTTAR PURV ROOM NO.2 NEAR GHANTAGHAR</t>
-  </si>
-  <si>
     <t>TOWN HALL UTTAR PURV ROOM NO.3 NEAR GHANTAGHAR</t>
   </si>
   <si>
@@ -892,7 +961,7 @@
     <t>FAIZ A AAM INTER COLLEGE PURVI BHAG ROOM NO.2</t>
   </si>
   <si>
-    <t>### # ## ##0 ##### ###### ### #0 ##0.3</t>
+    <t>DHARAMSHALA SARNEEMAL ROOM NO.2 NIKAT NIGAR CINEMA</t>
   </si>
   <si>
     <t>FAIZ A AAM INTER COLLEGE PURVI BHAG ROOM NO.4</t>
@@ -968,9 +1037,6 @@
   </si>
   <si>
     <t>DHARMSHALA SARNEEMAL ROOM NO.1 NIKAT NIGAR CINEMA</t>
-  </si>
-  <si>
-    <t>DHARAMSHALA SARNEEMAL ROOM NO.2 NIKAT NIGAR CINEMA</t>
   </si>
   <si>
     <t>DHARAMSHALA SARNEEMAL ROOM NO.3 NIKAT NIGAR CINEMA</t>
@@ -1148,8 +1214,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1165,7 +1239,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1173,12 +1247,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1477,88 +1569,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="E2" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="F2" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="G2" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="H2" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="J2" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="K2" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="L2" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="M2" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="N2" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="O2" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="P2" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="Q2" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="R2" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="S2" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="T2" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="U2" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="V2" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="W2" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="X2" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="Y2" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="Z2" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1566,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1646,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1726,7 +1893,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1806,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1886,7 +2053,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1966,7 +2133,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2046,7 +2213,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2126,7 +2293,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2206,7 +2373,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2286,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2366,7 +2533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2446,7 +2613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2526,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2606,7 +2773,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2686,7 +2853,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2766,7 +2933,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2846,7 +3013,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2926,7 +3093,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3006,7 +3173,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3086,7 +3253,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3166,7 +3333,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3246,7 +3413,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3326,7 +3493,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3406,7 +3573,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3486,7 +3653,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3566,7 +3733,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3646,7 +3813,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3726,7 +3893,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3806,7 +3973,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3886,7 +4053,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3966,7 +4133,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4046,7 +4213,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4126,7 +4293,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4206,7 +4373,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4286,7 +4453,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4366,7 +4533,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4446,7 +4613,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4526,7 +4693,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4606,7 +4773,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -4686,7 +4853,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4766,7 +4933,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4846,7 +5013,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4926,7 +5093,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5006,7 +5173,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5086,7 +5253,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -5166,7 +5333,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5246,7 +5413,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -5326,7 +5493,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5406,7 +5573,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5486,7 +5653,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5566,7 +5733,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5646,7 +5813,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5726,7 +5893,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -5806,7 +5973,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5886,7 +6053,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5966,7 +6133,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -6046,7 +6213,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6126,7 +6293,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -6206,7 +6373,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -6286,7 +6453,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -6366,7 +6533,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -6446,7 +6613,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6526,7 +6693,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6606,7 +6773,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6686,7 +6853,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6766,7 +6933,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6846,7 +7013,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6926,7 +7093,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -7006,7 +7173,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -7086,7 +7253,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -7166,7 +7333,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -7246,7 +7413,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7326,7 +7493,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7406,7 +7573,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -7486,7 +7653,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -7566,7 +7733,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7646,7 +7813,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7726,7 +7893,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -7806,7 +7973,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7886,7 +8053,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -7966,7 +8133,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -8046,7 +8213,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -8126,7 +8293,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -8206,7 +8373,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -8286,7 +8453,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -8366,7 +8533,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -8446,7 +8613,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -8526,7 +8693,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -8606,7 +8773,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -8686,7 +8853,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -8766,7 +8933,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -8846,7 +9013,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8926,7 +9093,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -9006,7 +9173,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -9086,7 +9253,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -9166,7 +9333,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -9246,7 +9413,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -9326,7 +9493,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -9406,7 +9573,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -9486,7 +9653,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -9566,7 +9733,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -9646,7 +9813,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -9726,7 +9893,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -9806,7 +9973,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -9886,7 +10053,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -9966,7 +10133,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -10046,7 +10213,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -10126,7 +10293,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -10206,7 +10373,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -10286,7 +10453,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -10366,7 +10533,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -10446,7 +10613,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -10526,7 +10693,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -10606,7 +10773,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -10686,7 +10853,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -10766,7 +10933,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -10846,7 +11013,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -10926,7 +11093,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11006,7 +11173,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11086,7 +11253,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11166,7 +11333,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11246,7 +11413,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11326,7 +11493,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -11406,7 +11573,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -11486,7 +11653,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -11566,7 +11733,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -11646,7 +11813,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -11726,7 +11893,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -11806,7 +11973,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -11886,7 +12053,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -11966,7 +12133,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12046,7 +12213,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12126,7 +12293,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -12206,7 +12373,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12286,7 +12453,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12366,7 +12533,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12446,7 +12613,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12526,7 +12693,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -12606,7 +12773,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12686,7 +12853,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12766,7 +12933,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12846,7 +13013,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12926,7 +13093,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -13006,7 +13173,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -13086,7 +13253,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -13166,7 +13333,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -13246,7 +13413,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -13326,7 +13493,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -13406,7 +13573,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -13486,7 +13653,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -13566,7 +13733,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -13646,7 +13813,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -13726,7 +13893,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -13806,7 +13973,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -13886,7 +14053,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -13966,7 +14133,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -14046,7 +14213,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -14126,7 +14293,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -14206,7 +14373,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -14286,7 +14453,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -14366,7 +14533,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -14446,7 +14613,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -14526,7 +14693,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -14606,7 +14773,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -14686,7 +14853,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -14766,7 +14933,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -14846,7 +15013,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -14926,7 +15093,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -15006,7 +15173,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -15086,7 +15253,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -15166,7 +15333,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -15246,7 +15413,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -15326,7 +15493,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -15406,7 +15573,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -15486,7 +15653,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -15566,7 +15733,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -15646,7 +15813,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -15726,7 +15893,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -15806,7 +15973,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -15886,7 +16053,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -15966,7 +16133,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -16046,7 +16213,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -16126,7 +16293,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -16206,7 +16373,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -16286,7 +16453,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -16366,7 +16533,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -16446,7 +16613,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -16526,7 +16693,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -16606,7 +16773,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -16686,7 +16853,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -16766,7 +16933,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -16846,7 +17013,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -16926,7 +17093,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -17006,7 +17173,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -17086,7 +17253,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -17166,7 +17333,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -17246,7 +17413,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -17326,7 +17493,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -17406,7 +17573,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -17486,7 +17653,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -17566,7 +17733,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -17646,7 +17813,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -17726,7 +17893,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -17806,7 +17973,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -17886,7 +18053,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -17966,7 +18133,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -18046,7 +18213,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -18126,7 +18293,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -18206,7 +18373,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -18286,7 +18453,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -18366,7 +18533,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -18446,7 +18613,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -18526,7 +18693,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -18606,7 +18773,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -18686,7 +18853,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -18766,7 +18933,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -18846,7 +19013,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -18926,7 +19093,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -19006,7 +19173,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -19086,7 +19253,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -19166,7 +19333,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -19246,7 +19413,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -19326,7 +19493,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -19406,7 +19573,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -19486,7 +19653,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -19566,7 +19733,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -19646,7 +19813,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -19726,7 +19893,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -19806,7 +19973,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -19886,7 +20053,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -19966,7 +20133,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -20046,7 +20213,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -20126,7 +20293,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -20206,7 +20373,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -20286,7 +20453,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -20366,7 +20533,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -20446,7 +20613,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -20526,7 +20693,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -20606,7 +20773,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -20686,7 +20853,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -20766,7 +20933,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -20846,7 +21013,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -20926,7 +21093,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -21006,7 +21173,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -21086,7 +21253,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -21166,7 +21333,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -21246,7 +21413,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -21326,7 +21493,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -21406,7 +21573,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -21486,7 +21653,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -21566,7 +21733,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -21646,7 +21813,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -21726,7 +21893,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -21806,7 +21973,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -21886,7 +22053,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -21966,7 +22133,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -22046,7 +22213,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -22126,7 +22293,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -22206,7 +22373,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -22286,7 +22453,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -22366,7 +22533,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -22446,7 +22613,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -22526,7 +22693,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -22606,7 +22773,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -22686,7 +22853,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -22766,7 +22933,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -22846,7 +23013,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -22926,7 +23093,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -23006,7 +23173,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -23086,7 +23253,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -23166,7 +23333,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -23246,7 +23413,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -23326,7 +23493,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -23406,7 +23573,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -23486,7 +23653,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -23566,7 +23733,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -23646,7 +23813,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -23726,7 +23893,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -23806,7 +23973,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -23886,7 +24053,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -23966,7 +24133,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -24046,7 +24213,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -24126,7 +24293,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -24206,7 +24373,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -24286,7 +24453,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -24366,7 +24533,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -24446,7 +24613,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -24526,7 +24693,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -24606,7 +24773,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -24686,7 +24853,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -24766,7 +24933,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -24846,7 +25013,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -24926,7 +25093,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -25006,7 +25173,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -25086,7 +25253,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -25166,7 +25333,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -25246,7 +25413,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -25326,7 +25493,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -25406,7 +25573,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -25486,7 +25653,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -25566,7 +25733,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -25646,7 +25813,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -25726,7 +25893,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -25806,7 +25973,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -25886,7 +26053,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -25966,7 +26133,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -26046,7 +26213,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -26126,7 +26293,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -26206,7 +26373,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -26286,7 +26453,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -26366,7 +26533,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -26446,7 +26613,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -26526,7 +26693,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -26606,7 +26773,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -26686,7 +26853,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -26766,7 +26933,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -26846,7 +27013,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -26926,7 +27093,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -27006,7 +27173,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -27086,7 +27253,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -27166,7 +27333,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -27246,7 +27413,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -27326,7 +27493,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -27406,7 +27573,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -27486,7 +27653,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -27566,7 +27733,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -27646,7 +27813,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -27726,7 +27893,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -27806,7 +27973,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -27886,7 +28053,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -27966,7 +28133,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -28046,7 +28213,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -28126,7 +28293,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -28206,7 +28373,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -28286,7 +28453,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -28366,7 +28533,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -28446,7 +28613,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -28526,7 +28693,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -28606,7 +28773,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -28686,7 +28853,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -28766,7 +28933,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -28846,7 +29013,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -28926,7 +29093,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -29006,7 +29173,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -29086,7 +29253,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -29166,7 +29333,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -29246,7 +29413,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -29326,7 +29493,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -29406,7 +29573,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -29486,7 +29653,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -29566,7 +29733,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>0</v>
